--- a/notebooks/excluded.xlsx
+++ b/notebooks/excluded.xlsx
@@ -1,34 +1,146 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+  <si>
+    <t>работа</t>
+  </si>
+  <si>
+    <t>почему выкинул</t>
+  </si>
+  <si>
+    <t>ссылка</t>
+  </si>
+  <si>
+    <t>Vikhr (MRL 2024)</t>
+  </si>
+  <si>
+    <t>ruT5 / ruBERT (Zmitrovich и др.)</t>
+  </si>
+  <si>
+    <t>PAE</t>
+  </si>
+  <si>
+    <t>Habr, ecom.tech</t>
+  </si>
+  <si>
+    <t>UIE (ACL 2022)</t>
+  </si>
+  <si>
+    <t>OA-Mine (WWW 2022)</t>
+  </si>
+  <si>
+    <t>GPT-3 (NeurIPS 2020)</t>
+  </si>
+  <si>
+    <t>Parallel Decoding (Amazon)</t>
+  </si>
+  <si>
+    <t>Explicit Attribute Extraction in e-Commerce Search (ECNLP 2024)</t>
+  </si>
+  <si>
+    <t>Sabeh и др. Exploring LLMs for Product Attribute Value Identification (arXiv 2024)</t>
+  </si>
+  <si>
+    <t>Geng и др., JSONSchemaBench (arXiv 2025)</t>
+  </si>
+  <si>
+    <t>Singh и др., Structured Output Benchmark (arXiv 2026)</t>
+  </si>
+  <si>
+    <t>Кулиев, Habr (RWB), 2025</t>
+  </si>
+  <si>
+    <t>статью отозвали, в таблице 6 ошибка</t>
+  </si>
+  <si>
+    <t>модели общего назначения, про атрибуты ничего</t>
+  </si>
+  <si>
+    <t>извлекает из PDF с трендами моды, а не из описаний</t>
+  </si>
+  <si>
+    <t>про сопоставление товаров, не про извлечение</t>
+  </si>
+  <si>
+    <t>общее извлечение, не про товары</t>
+  </si>
+  <si>
+    <t>атрибуты заранее не заданы, а у нас заданы</t>
+  </si>
+  <si>
+    <t>общий фон, few-shot смотрим в ExtractGPT</t>
+  </si>
+  <si>
+    <t>нет даты и площадки, данные закрыты</t>
+  </si>
+  <si>
+    <t>извлекает из поисковых запросов, а не из описаний</t>
+  </si>
+  <si>
+    <t>промптинг LLaMA/Mistral для извлечения, близко к ExtractGPT и Brinkmann; в запас, лимит 10-15</t>
+  </si>
+  <si>
+    <t>про способы ограниченного декодирования (формат ответа модели), а обзор про качество извлечения; формат ответа проверяется в собственном эксперименте</t>
+  </si>
+  <si>
+    <t>про формат ответа модели на общих данных, не про извлечение атрибутов из товаров; формат проверяется в собственном эксперименте</t>
+  </si>
+  <si>
+    <t>не рецензируется; метрики относятся ко всему конвейеру сопоставления товаров, а не к извлечению атрибутов</t>
+  </si>
+  <si>
+    <t>https://aclanthology.org/2024.ecnlp-1.13/</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2409.12695</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2501.10868</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2604.25359</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/911210</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <scheme val="minor"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -43,84 +155,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,147 +459,148 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>работа</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>почему выкинул</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Vikhr (MRL 2024)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>статью отозвали, в таблице 6 ошибка</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ruT5 / ruBERT (Zmitrovich и др.)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>модели общего назначения, про атрибуты ничего</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PAE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>извлекает из PDF с трендами моды, а не из описаний</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Habr, ecom.tech</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>про сопоставление товаров, не про извлечение</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>UIE (ACL 2022)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>общее извлечение, не про товары</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>OA-Mine (WWW 2022)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>атрибуты заранее не заданы, а у нас заданы</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>GPT-3 (NeurIPS 2020)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>общий фон, few-shot смотрим в ExtractGPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Parallel Decoding (Amazon)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>нет даты и площадки, данные закрыты</t>
-        </is>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <hyperlinks>
+    <hyperlink ref="C10" r:id="rId1"/>
+    <hyperlink ref="C11" r:id="rId2"/>
+    <hyperlink ref="C12" r:id="rId3"/>
+    <hyperlink ref="C13" r:id="rId4"/>
+    <hyperlink ref="C14" r:id="rId5"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>